--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>同胞内出生順（長男、長女など）をFamilyMemberHistoryに付記するための拡張。valueは CodeableConcept で、JP_SiblingOrder_VS のコード（SO1, SO1F など）を推奨する。</t>
+    <t>同胞内出生順（長男、長女など）をFamilyMemberHistoryに付記するための拡張。同胞はvalueは CodeableConcept で、JP_SiblingOrder_VS のコード（SO1, SO1F など）を推奨する。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -331,10 +331,10 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Extension.extension:siblingOrder</t>
-  </si>
-  <si>
-    <t>siblingOrder</t>
+    <t>Extension.extension:siblingBirthOrder</t>
+  </si>
+  <si>
+    <t>siblingBirthOrder</t>
   </si>
   <si>
     <t>Y</t>
@@ -346,13 +346,13 @@
     <t>同胞内での出生順を表現した数値。性別に関係なく、単純に出生順を示す。例えば、男、男、女の出生順の場合、長男は1、次男は2、長女は3など。</t>
   </si>
   <si>
-    <t>Extension.extension:siblingOrder.id</t>
+    <t>Extension.extension:siblingBirthOrder.id</t>
   </si>
   <si>
     <t>Extension.extension.id</t>
   </si>
   <si>
-    <t>Extension.extension:siblingOrder.extension</t>
+    <t>Extension.extension:siblingBirthOrder.extension</t>
   </si>
   <si>
     <t>Extension.extension.extension</t>
@@ -361,7 +361,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Extension.extension:siblingOrder.url</t>
+    <t>Extension.extension:siblingBirthOrder.url</t>
   </si>
   <si>
     <t>Extension.extension.url</t>
@@ -386,7 +386,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Extension.extension:siblingOrder.value[x]</t>
+    <t>Extension.extension:siblingBirthOrder.value[x]</t>
   </si>
   <si>
     <t>Extension.extension.value[x]</t>
@@ -409,10 +409,10 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:genderedSiblingOrder</t>
-  </si>
-  <si>
-    <t>genderedSiblingOrder</t>
+    <t>Extension.extension:genderedSiblingBirthOrder</t>
+  </si>
+  <si>
+    <t>genderedSiblingBirthOrder</t>
   </si>
   <si>
     <t>性別同胞内出生順</t>
@@ -421,16 +421,16 @@
     <t>同胞内での出生順を性別に表現した用語。用語で出生順が表現されており、用語選択のみで表現される（例：長男、長女など）。</t>
   </si>
   <si>
-    <t>Extension.extension:genderedSiblingOrder.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:genderedSiblingOrder.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:genderedSiblingOrder.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:genderedSiblingOrder.value[x]</t>
+    <t>Extension.extension:genderedSiblingBirthOrder.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:genderedSiblingBirthOrder.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:genderedSiblingBirthOrder.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:genderedSiblingBirthOrder.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -774,9 +774,9 @@
   <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.8515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.9921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.2265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.0" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>同胞内出生順（長男、長女など）をFamilyMemberHistoryに付記するための拡張。同胞はvalueは CodeableConcept で、JP_SiblingOrder_VS のコード（SO1, SO1F など）を推奨する。</t>
+    <t>同胞内出生順（長男、長女など）をFamilyMemberHistoryに付記するための拡張。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -265,7 +265,7 @@
     <t>同胞内出生順</t>
   </si>
   <si>
-    <t>FamilyMemberHistory リソース全体に対して、関連する家族成員の同胞内出生順を表現する拡張。日本語での表現（長男、長女、次男など）を CodeableConcept で提供する。この拡張は社会学的・文化的文脈で利用され、医学的な遺伝情報とは独立している。家系図はスコープ外。</t>
+    <t>FamilyMemberHistoryのrelationship（続柄）と組み合わせて、関連する家族成員の同胞内出生順を表現する拡張。同胞内の順位を整数で、性別の同胞内の出生準名（長男、長女、次男、次女など）を CodeableConcept で表現する。この拡張は社会学的・文化的文脈で利用され、医学的な遺伝情報とは独立している。遺伝学的家系図はスコープ外。</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -415,10 +415,10 @@
     <t>genderedSiblingBirthOrder</t>
   </si>
   <si>
-    <t>性別同胞内出生順</t>
-  </si>
-  <si>
-    <t>同胞内での出生順を性別に表現した用語。用語で出生順が表現されており、用語選択のみで表現される（例：長男、長女など）。</t>
+    <t>性別同胞内出生順名称（用語）</t>
+  </si>
+  <si>
+    <t>同胞内の性別の出生順を表す用語（例：長男、長女、次男、次女）。</t>
   </si>
   <si>
     <t>Extension.extension:genderedSiblingBirthOrder.id</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-familymemberhistory-siblingorder.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder</t>
+    <t>http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_FamilyMemberHistory_SiblingOrder</t>
   </si>
   <si>
     <t>Version</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>同胞内出生順（長男、長女など）をFamilyMemberHistoryに付記するための拡張。</t>
+    <t>同胞内順位をFamilyMemberHistoryに付記するための拡張。</t>
   </si>
   <si>
     <t>Purpose</t>
